--- a/output/reports/cv_experiment_DecisionTree_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.057622671127319</v>
+        <v>0.04854393005371094</v>
       </c>
       <c r="E2" t="n">
-        <v>0.830471764728422</v>
+        <v>0.9918638006855159</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8538130225487712</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8524453382050456</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8879177709925241</v>
+        <v>0.9796368572883082</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.685253381729126</v>
+        <v>0.05994701385498047</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8404319695107754</v>
+        <v>0.9902363723372692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8538130225487712</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8524453382050456</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8879177709925241</v>
+        <v>0.9796368572883082</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.057622671127319</v>
+        <v>0.04854393005371094</v>
       </c>
       <c r="E2" t="n">
-        <v>0.830471764728422</v>
+        <v>0.9918638006855159</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8538130225487712</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8524453382050456</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8879177709925241</v>
+        <v>0.9796368572883082</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.685253381729126</v>
+        <v>0.05994701385498047</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8404319695107754</v>
+        <v>0.9902363723372692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8538130225487712</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8524453382050456</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8879177709925241</v>
+        <v>0.9796368572883082</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': None, 'max_depth': None, 'criterion': 'entropy'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04854393005371094</v>
+        <v>0.6422059535980225</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9918638006855159</v>
+        <v>0.5878335824340218</v>
       </c>
       <c r="F2" t="n">
-        <v>0.974025974025974</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9738673001866622</v>
+        <v>0.6376104568244306</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9796368572883082</v>
+        <v>0.7747504309106579</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05994701385498047</v>
+        <v>1.085945844650269</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9902363723372692</v>
+        <v>0.6102692566451896</v>
       </c>
       <c r="F3" t="n">
-        <v>0.974025974025974</v>
+        <v>0.652542372881356</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9738673001866622</v>
+        <v>0.6134064304253403</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9796368572883082</v>
+        <v>0.739406779661017</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04854393005371094</v>
+        <v>0.6422059535980225</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9918638006855159</v>
+        <v>0.5878335824340218</v>
       </c>
       <c r="F2" t="n">
-        <v>0.974025974025974</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9738673001866622</v>
+        <v>0.6376104568244306</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9796368572883082</v>
+        <v>0.7747504309106579</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05994701385498047</v>
+        <v>1.085945844650269</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9902363723372692</v>
+        <v>0.6102692566451896</v>
       </c>
       <c r="F3" t="n">
-        <v>0.974025974025974</v>
+        <v>0.652542372881356</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9738673001866622</v>
+        <v>0.6134064304253403</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9796368572883082</v>
+        <v>0.739406779661017</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 7, 'criterion': 'gini'}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
